--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dispensation-medicaments.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dispensation-medicaments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2727" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="311">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -511,6 +511,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -700,6 +703,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -710,10 +716,25 @@
     <t>Texte de la section</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -726,6 +747,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -736,6 +766,9 @@
     <t>Auteur de la section</t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -743,6 +776,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -896,6 +932,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1272,7 +1314,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4311,7 +4353,9 @@
       <c r="K30" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4382,10 +4426,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4419,7 +4463,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>74</v>
@@ -4441,7 +4485,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4459,7 +4503,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4479,10 +4523,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4516,7 +4560,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4538,7 +4582,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4556,7 +4600,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4576,10 +4620,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4593,7 +4637,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4605,10 +4649,10 @@
         <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4659,7 +4703,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4679,10 +4723,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4696,7 +4740,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4705,13 +4749,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4762,7 +4806,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4782,10 +4826,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4883,10 +4927,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4915,7 +4959,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4927,7 +4971,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -4966,7 +5010,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4986,17 +5030,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -5018,7 +5062,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5030,7 +5074,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5069,7 +5113,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5089,17 +5133,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5121,7 +5165,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5133,7 +5177,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5172,7 +5216,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5192,17 +5236,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5224,7 +5268,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5275,7 +5319,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5295,17 +5339,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -5327,7 +5371,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5339,7 +5383,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5378,7 +5422,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5398,10 +5442,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5424,11 +5468,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5479,7 +5523,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5499,10 +5543,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5529,7 +5573,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5580,7 +5624,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5600,17 +5644,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5628,11 +5672,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5683,7 +5727,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5703,17 +5747,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5731,11 +5775,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5786,7 +5830,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5806,17 +5850,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5834,11 +5878,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5889,7 +5933,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5909,10 +5953,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5926,7 +5970,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5935,16 +5979,18 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -5992,7 +6038,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6012,10 +6058,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6029,7 +6075,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6038,15 +6084,17 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -6095,7 +6143,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6115,10 +6163,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6141,12 +6189,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6194,7 +6246,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6214,10 +6266,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6242,10 +6294,14 @@
       <c r="K49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
@@ -6273,7 +6329,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6291,7 +6347,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6311,10 +6367,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6337,12 +6393,18 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
       </c>
@@ -6390,7 +6452,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6410,10 +6472,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6427,7 +6489,7 @@
         <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -6436,16 +6498,18 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -6493,7 +6557,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6513,10 +6577,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6539,12 +6603,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6592,7 +6658,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6612,10 +6678,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6629,7 +6695,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6638,10 +6704,10 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -6693,7 +6759,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6713,10 +6779,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6814,10 +6880,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6915,10 +6981,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7016,10 +7082,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7117,10 +7183,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7220,10 +7286,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7323,10 +7389,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7426,10 +7492,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7529,10 +7595,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7630,10 +7696,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7663,7 +7729,7 @@
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
@@ -7689,7 +7755,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7707,7 +7773,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7727,10 +7793,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7764,7 +7830,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>74</v>
@@ -7806,7 +7872,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7826,10 +7892,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7852,7 +7918,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7905,7 +7971,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7925,10 +7991,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7951,7 +8017,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8004,7 +8070,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8024,10 +8090,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8050,7 +8116,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8103,7 +8169,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8123,10 +8189,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8149,7 +8215,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8202,7 +8268,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8222,10 +8288,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8248,7 +8314,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8301,7 +8367,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8321,10 +8387,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8347,7 +8413,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8400,7 +8466,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8420,10 +8486,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8446,7 +8512,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8499,7 +8565,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8519,10 +8585,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8545,7 +8611,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8598,7 +8664,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8618,10 +8684,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8644,7 +8710,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8697,7 +8763,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8717,10 +8783,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8743,12 +8809,16 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>74</v>
       </c>
@@ -8796,7 +8866,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8816,10 +8886,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8917,10 +8987,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9018,10 +9088,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9119,10 +9189,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9220,10 +9290,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9323,10 +9393,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9426,10 +9496,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9529,10 +9599,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9632,10 +9702,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9733,10 +9803,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9763,7 +9833,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9772,7 +9842,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>74</v>
@@ -9814,7 +9884,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9834,10 +9904,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9871,7 +9941,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>74</v>
@@ -9913,7 +9983,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -9933,10 +10003,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -9959,7 +10029,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10012,7 +10082,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
